--- a/docs/result/row-data/3rd-test/pessimistic/pessimistic-lock-800-ngrinder-result.xlsx
+++ b/docs/result/row-data/3rd-test/pessimistic/pessimistic-lock-800-ngrinder-result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sangja/Projects/concurrency-control-benchmarks/docs/result/row-data/3rd-test/pessimistic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FAE090-D750-044C-8B8A-0FF7731A7E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC414646-38D0-9645-A2F1-11244039A69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14700" yWindow="660" windowWidth="14700" windowHeight="18460" xr2:uid="{9E9157CD-8F9C-A94B-81A0-86877F03A130}"/>
   </bookViews>
@@ -742,8 +742,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="268407" cy="345992"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -828,7 +828,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -896,8 +896,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="279628" cy="345992"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="20" name="TextBox 19">
@@ -982,7 +982,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="20" name="TextBox 19">
@@ -1050,8 +1050,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="185692" cy="345992"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="TextBox 20">
@@ -1136,7 +1136,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="TextBox 20">
@@ -1204,8 +1204,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="453907" cy="345992"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="TextBox 21">
@@ -1321,7 +1321,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="TextBox 21">
@@ -1389,8 +1389,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1049454" cy="359009"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="TextBox 22">
@@ -1559,7 +1559,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="TextBox 22">
@@ -1627,8 +1627,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="806503" cy="359009"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="TextBox 23">
@@ -1766,7 +1766,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="TextBox 23">
@@ -1834,8 +1834,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1303947" cy="498929"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="TextBox 24">
@@ -2126,7 +2126,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="TextBox 24">
@@ -2194,8 +2194,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="241300" cy="527004"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="TextBox 25">
@@ -2291,7 +2291,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="TextBox 25">
@@ -2362,8 +2362,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="253787" cy="527324"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="27" name="TextBox 26">
@@ -2459,7 +2459,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="27" name="TextBox 26">
@@ -2530,8 +2530,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1056379" cy="281214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="28" name="TextBox 27">
@@ -2739,7 +2739,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="28" name="TextBox 27">
@@ -2825,8 +2825,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="726930" cy="264885"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="29" name="TextBox 28">
@@ -2972,7 +2972,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="29" name="TextBox 28">
@@ -3043,8 +3043,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1014380" cy="244929"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="30" name="TextBox 29">
@@ -3240,7 +3240,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="30" name="TextBox 29">
@@ -3308,8 +3308,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1759858" cy="498929"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -3665,7 +3665,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -3733,8 +3733,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2239972" cy="248557"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="32" name="TextBox 31">
@@ -3957,7 +3957,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="32" name="TextBox 31">
@@ -4025,8 +4025,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1559722" cy="553357"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -4241,7 +4241,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -4309,8 +4309,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1559722" cy="453572"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="34" name="TextBox 33">
@@ -4502,7 +4502,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="34" name="TextBox 33">
@@ -4570,8 +4570,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2071786" cy="182999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="35" name="TextBox 34">
@@ -4726,7 +4726,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="35" name="TextBox 34">
@@ -4782,6 +4782,1476 @@
                 <a:t>"</a:t>
               </a:r>
               <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="738151" cy="355097"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="TextBox 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7595CE48-817E-AD4A-9DAD-6B9DB4B497AB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="4114800"/>
+              <a:ext cx="738151" cy="355097"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="TextBox 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7595CE48-817E-AD4A-9DAD-6B9DB4B497AB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="4114800"/>
+              <a:ext cx="738151" cy="355097"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(𝑛_𝑖−1) </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑖^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1599284" cy="182871"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C841AC8E-9510-2045-95A7-E0D00522EB1A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="5486400"/>
+              <a:ext cx="1599284" cy="182871"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑆</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑤𝑖𝑡h𝑖𝑛</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Σ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C841AC8E-9510-2045-95A7-E0D00522EB1A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="5486400"/>
+              <a:ext cx="1599284" cy="182871"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆𝑆_𝑤𝑖𝑡ℎ𝑖𝑛=Σ_(𝑖=1)^2 (𝑛_𝑖−1) 𝜎_𝑖^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="964816" cy="177228"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="TextBox 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13BA1BA9-6674-814D-983E-C0C693B993EB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="5943600"/>
+              <a:ext cx="964816" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑖</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="TextBox 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13BA1BA9-6674-814D-983E-C0C693B993EB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="5943600"/>
+              <a:ext cx="964816" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛_𝑖 (𝜇_𝑖−𝜇_𝑡𝑜𝑡𝑎𝑙 )^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1984902" cy="186782"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="TextBox 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3221FD86-63A5-F747-BA8C-A9CDACC1DAB0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="7315200"/>
+              <a:ext cx="1984902" cy="186782"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑆</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑏𝑒𝑡𝑤𝑒𝑒𝑛</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Σ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑘</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑖</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="TextBox 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3221FD86-63A5-F747-BA8C-A9CDACC1DAB0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="7315200"/>
+              <a:ext cx="1984902" cy="186782"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆𝑆_𝑏𝑒𝑡𝑤𝑒𝑒𝑛=Σ_(𝑖=1)^𝑘 𝑛_𝑖 (𝜇_𝑖−𝜇_𝑡𝑜𝑡𝑎𝑙 )^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1842235" cy="500137"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="TextBox 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F766CDD-76CA-FE4C-80CA-3B70F50B940E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="7772400"/>
+              <a:ext cx="1842235" cy="500137"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>total</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:rad>
+                      <m:radPr>
+                        <m:degHide m:val="on"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:radPr>
+                      <m:deg/>
+                      <m:e>
+                        <m:f>
+                          <m:fPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:fPr>
+                          <m:num>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>SS</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>within</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>SS</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>between</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:num>
+                          <m:den>
+                            <m:r>
+                              <m:rPr>
+                                <m:sty m:val="p"/>
+                              </m:rPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>N</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−1</m:t>
+                            </m:r>
+                          </m:den>
+                        </m:f>
+                      </m:e>
+                    </m:rad>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="TextBox 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F766CDD-76CA-FE4C-80CA-3B70F50B940E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="7772400"/>
+              <a:ext cx="1842235" cy="500137"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>total=√((SS_within+SS_between)/(N−1))</a:t>
+              </a:r>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="438710" cy="173766"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7" name="TextBox 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68F900AD-9FB9-154C-937B-6E123A61CB7E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="8458200"/>
+              <a:ext cx="438710" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>2</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7" name="TextBox 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68F900AD-9FB9-154C-937B-6E123A61CB7E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="8458200"/>
+              <a:ext cx="438710" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>2𝜎_𝑡𝑜𝑡𝑎𝑙</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5115,7 +6585,7 @@
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -5416,289 +6886,363 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12">
-        <f>C2</f>
+        <f t="shared" ref="A12:A17" si="0">C2</f>
         <v>187</v>
       </c>
       <c r="B12">
-        <f>E2</f>
+        <f t="shared" ref="B12:C17" si="1">E2</f>
         <v>820.92499999999995</v>
       </c>
       <c r="C12">
-        <f>F2</f>
+        <f t="shared" si="1"/>
         <v>340.697</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13">
-        <f>C3</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B13">
-        <f>E3</f>
+        <f t="shared" si="1"/>
         <v>241.61500000000001</v>
       </c>
       <c r="C13">
-        <f>F3</f>
+        <f t="shared" si="1"/>
         <v>259.38200000000001</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14">
-        <f>C4</f>
+        <f t="shared" si="0"/>
         <v>386</v>
       </c>
       <c r="B14">
-        <f>E4</f>
+        <f t="shared" si="1"/>
         <v>1183.296</v>
       </c>
       <c r="C14">
-        <f>F4</f>
+        <f t="shared" si="1"/>
         <v>484.72800000000001</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15">
-        <f>C5</f>
+        <f t="shared" si="0"/>
         <v>211</v>
       </c>
       <c r="B15">
-        <f>E5</f>
+        <f t="shared" si="1"/>
         <v>992.31799999999998</v>
       </c>
       <c r="C15">
-        <f>F5</f>
+        <f t="shared" si="1"/>
         <v>302.40199999999999</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16">
-        <f>C6</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B16">
-        <f>E6</f>
+        <f t="shared" si="1"/>
         <v>10.5</v>
       </c>
       <c r="C16">
-        <f>F6</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:5">
       <c r="A17">
-        <f>C7</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="B17">
-        <f>E7</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="C17">
-        <f>F7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:5">
       <c r="B19">
-        <f t="shared" ref="B19:B24" si="0">A12*B12</f>
+        <f t="shared" ref="B19:B24" si="2">A12*B12</f>
         <v>153512.97500000001</v>
       </c>
+      <c r="E19">
+        <f t="shared" ref="E19:E24" si="3">(A12-1)*POWER(C12,2)</f>
+        <v>21589846.920474</v>
+      </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:5">
       <c r="B20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3140.9949999999999</v>
       </c>
+      <c r="E20">
+        <f t="shared" si="3"/>
+        <v>807348.26308800001</v>
+      </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:5">
       <c r="B21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>456752.25599999999</v>
       </c>
+      <c r="E21">
+        <f t="shared" si="3"/>
+        <v>90460075.083840013</v>
+      </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:5">
       <c r="B22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>209379.098</v>
       </c>
+      <c r="E22">
+        <f t="shared" si="3"/>
+        <v>19203863.616840001</v>
+      </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:5">
       <c r="B23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
+      <c r="E23">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:5">
       <c r="B24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
+      <c r="E24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:5">
       <c r="B25">
         <f>SUM(B19:B24)</f>
         <v>822819.32400000002</v>
       </c>
+      <c r="E25">
+        <f>SUM(E19:E24)</f>
+        <v>132061134.13424201</v>
+      </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:5">
       <c r="B26">
         <f>SUM(A12:A17)</f>
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="B27">
         <f>B25/B26</f>
         <v>1028.5241550000001</v>
       </c>
+      <c r="E27">
+        <f>A12*POWER((B12-B$27),2)</f>
+        <v>8059215.5123055317</v>
+      </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5">
       <c r="B28">
         <f>ROUND(B27,2)</f>
         <v>1028.52</v>
       </c>
+      <c r="E28">
+        <f t="shared" ref="E28:E32" si="4">A13*POWER((B13-B$27),2)</f>
+        <v>8049938.2368965829</v>
+      </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="29" spans="1:5">
+      <c r="E29">
+        <f t="shared" si="4"/>
+        <v>9246369.0658157524</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="B30">
-        <f t="shared" ref="B30:B35" si="1">POWER(C12,2)</f>
+        <f t="shared" ref="B30:B35" si="5">POWER(C12,2)</f>
         <v>116074.445809</v>
       </c>
+      <c r="E30">
+        <f t="shared" si="4"/>
+        <v>276596.8742355305</v>
+      </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:5">
       <c r="B31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>67279.021924000001</v>
       </c>
+      <c r="E31">
+        <f t="shared" si="4"/>
+        <v>2072746.3603269283</v>
+      </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:5">
       <c r="B32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>234961.23398400002</v>
       </c>
+      <c r="E32">
+        <f t="shared" si="4"/>
+        <v>1031289.3093884642</v>
+      </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:5">
       <c r="B33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>91446.969603999998</v>
       </c>
+      <c r="E33">
+        <f>SUM(E27:E32)</f>
+        <v>28736155.358968783</v>
+      </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:5">
       <c r="B34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:5">
       <c r="B35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="E35">
+        <f>SQRT((E25+E33)/(B26-1))</f>
+        <v>448.60692380035277</v>
+      </c>
     </row>
-    <row r="36" spans="2:2">
+    <row r="36" spans="2:5">
       <c r="B36">
-        <f t="shared" ref="B36:B41" si="2">POWER(B12,2)</f>
+        <f t="shared" ref="B36:B41" si="6">POWER(B12,2)</f>
         <v>673917.85562499997</v>
       </c>
+      <c r="E36">
+        <f>ROUND(E35,2)</f>
+        <v>448.61</v>
+      </c>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="2:5">
       <c r="B37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>58377.808225000008</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:5">
       <c r="B38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1400189.4236160002</v>
       </c>
+      <c r="E38">
+        <f>2*E35</f>
+        <v>897.21384760070555</v>
+      </c>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="2:5">
       <c r="B39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>984695.01312399993</v>
       </c>
+      <c r="E39">
+        <f>ROUND(E38,2)</f>
+        <v>897.21</v>
+      </c>
     </row>
-    <row r="40" spans="2:2">
+    <row r="40" spans="2:5">
       <c r="B40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>110.25</v>
       </c>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="2:5">
       <c r="B41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>169</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="2:5">
       <c r="B42">
-        <f t="shared" ref="B42:B47" si="3">B30+B36</f>
+        <f t="shared" ref="B42:B47" si="7">B30+B36</f>
         <v>789992.30143400002</v>
       </c>
     </row>
-    <row r="43" spans="2:2">
+    <row r="43" spans="2:5">
       <c r="B43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>125656.83014900002</v>
       </c>
     </row>
-    <row r="44" spans="2:2">
+    <row r="44" spans="2:5">
       <c r="B44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1635150.6576000003</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="2:5">
       <c r="B45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1076141.982728</v>
       </c>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="2:5">
       <c r="B46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>110.5</v>
       </c>
     </row>
-    <row r="47" spans="2:2">
+    <row r="47" spans="2:5">
       <c r="B47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>169</v>
       </c>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="2:5">
       <c r="B48">
-        <f t="shared" ref="B48:B53" si="4">A12*B42</f>
+        <f t="shared" ref="B48:B53" si="8">A12*B42</f>
         <v>147728560.36815801</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1633538.7919370001</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>631168153.83360004</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>227065958.35560802</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>221</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>169</v>
       </c>
     </row>
